--- a/04_모델산출물/v8_노선2/지표_노선2.xlsx
+++ b/04_모델산출물/v8_노선2/지표_노선2.xlsx
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1012,46 +1012,46 @@
         <v>0.3697</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7265</v>
+        <v>0.7186</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="O2" t="n">
-        <v>0.658</v>
+        <v>0.6597</v>
       </c>
       <c r="P2" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0589</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3024</v>
+        <v>0.2694</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6251</v>
+        <v>0.619</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0119</v>
+        <v>0.0114</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4909</v>
+        <v>0.4847</v>
       </c>
       <c r="V2" t="n">
-        <v>0.057</v>
+        <v>0.0417</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3422</v>
+        <v>0.3196</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6738</v>
+        <v>0.6635</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6233</v>
+        <v>0.6368</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6903</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1067,121 +1067,121 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0.013</v>
+        <v>0.0211</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0198</v>
+        <v>0.0406</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5706</v>
+        <v>0.5483</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0149</v>
+        <v>0.025</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0161</v>
+        <v>0.0228</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0075</v>
+        <v>0.0101</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6705</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="AL2" t="n">
-        <v>240.6</v>
+        <v>245.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.0299</v>
+        <v>8.1363</v>
       </c>
       <c r="AN2" t="n">
-        <v>181.4</v>
+        <v>203.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>13.0499</v>
+        <v>26.7339</v>
       </c>
       <c r="AP2" t="n">
-        <v>145.4</v>
+        <v>140.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.0299</v>
+        <v>8.1363</v>
       </c>
       <c r="AR2" t="n">
-        <v>476.6</v>
+        <v>454.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.0499</v>
+        <v>26.7339</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.6119</v>
+        <v>0.6145</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.0191</v>
+        <v>0.0053</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.7128</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0142</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.574</v>
+        <v>0.5566</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0127</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.3412</v>
+        <v>0.3215</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0193</v>
+        <v>0.0109</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.6727</v>
+        <v>0.6636</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0053</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.6885</v>
+        <v>0.6764</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0094</v>
+        <v>0.0062</v>
       </c>
       <c r="BF2" t="n">
-        <v>236.2</v>
+        <v>237.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.3621</v>
+        <v>2.0494</v>
       </c>
       <c r="BH2" t="n">
-        <v>175.4</v>
+        <v>189</v>
       </c>
       <c r="BI2" t="n">
-        <v>9.370200000000001</v>
+        <v>6.2849</v>
       </c>
       <c r="BJ2" t="n">
-        <v>149.8</v>
+        <v>148.8</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.3621</v>
+        <v>2.0494</v>
       </c>
       <c r="BL2" t="n">
-        <v>482.6</v>
+        <v>469</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.370200000000001</v>
+        <v>6.2849</v>
       </c>
       <c r="BN2" t="n">
         <v>25</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.3872</v>
+        <v>0.3618</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5431</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.5</v>
@@ -1202,19 +1202,19 @@
         <v>608</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.6653</v>
+        <v>0.6696</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.2114</v>
+        <v>0.1941</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.6212</v>
+        <v>0.6147</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.481</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.7614</v>
+        <v>0.7207</v>
       </c>
       <c r="CB2" t="n">
         <v>0.1908</v>
@@ -1223,19 +1223,19 @@
         <v>330</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.634</v>
+        <v>0.6309</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1497</v>
+        <v>0.1795</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.5828</v>
+        <v>0.5992</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.694</v>
+        <v>0.702</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.4716</v>
+        <v>0.4963</v>
       </c>
       <c r="CI2" t="n">
         <v>0.7544999999999999</v>
@@ -1244,19 +1244,19 @@
         <v>106</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.6968</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.277</v>
+        <v>0.2256</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.661</v>
+        <v>0.6351</v>
       </c>
       <c r="CN2" t="n">
         <v>0.5714</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.7506</v>
+        <v>0.6988</v>
       </c>
       <c r="CP2" t="n">
         <v>0.1981</v>
@@ -1265,19 +1265,19 @@
         <v>464</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.7136</v>
+        <v>0.7363</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.3135</v>
+        <v>0.3807</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.651</v>
+        <v>0.6881</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.4863</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.8157</v>
+        <v>0.8132</v>
       </c>
       <c r="CW2" t="n">
         <v>0.3147</v>
@@ -1286,19 +1286,19 @@
         <v>607</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.7487</v>
+        <v>0.767</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.3764</v>
+        <v>0.4336</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.6851</v>
+        <v>0.7159</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.5836</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.7867</v>
+        <v>0.7861</v>
       </c>
       <c r="DD2" t="n">
         <v>0.3822</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1356,46 +1356,46 @@
         <v>0.3697</v>
       </c>
       <c r="M3" t="n">
-        <v>0.756</v>
+        <v>0.7547</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0051</v>
+        <v>0.0081</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6776</v>
+        <v>0.6829</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0066</v>
+        <v>0.0069</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0784</v>
+        <v>0.0718</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3063</v>
+        <v>0.2819</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6423</v>
+        <v>0.6493</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0062</v>
+        <v>0.0067</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4453</v>
+        <v>0.4612</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0505</v>
+        <v>0.0418</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3742</v>
+        <v>0.3902</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6914</v>
+        <v>0.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6824</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7128</v>
+        <v>0.7176</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1411,121 +1411,121 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>0.0464</v>
+        <v>0.0254</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0361</v>
+        <v>0.018</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5788</v>
+        <v>0.5866</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0151</v>
+        <v>0.0112</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0101</v>
+        <v>0.0167</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0066</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.6969</v>
+        <v>0.7046</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0069</v>
+        <v>0.008</v>
       </c>
       <c r="AL3" t="n">
-        <v>258.6</v>
+        <v>263.4</v>
       </c>
       <c r="AM3" t="n">
-        <v>17.9109</v>
+        <v>9.8133</v>
       </c>
       <c r="AN3" t="n">
-        <v>189</v>
+        <v>185.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>23.7592</v>
+        <v>11.8406</v>
       </c>
       <c r="AP3" t="n">
-        <v>127.4</v>
+        <v>122.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.9109</v>
+        <v>9.8133</v>
       </c>
       <c r="AR3" t="n">
-        <v>469</v>
+        <v>472.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>23.7592</v>
+        <v>11.8406</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.6171</v>
+        <v>0.6425</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0171</v>
+        <v>0.0179</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.7842</v>
+        <v>0.7578</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0074</v>
+        <v>0.0072</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6087</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0056</v>
+        <v>0.0057</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.4026</v>
+        <v>0.3961</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0113</v>
+        <v>0.0128</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.7006</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0065</v>
+        <v>0.0072</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.7224</v>
+        <v>0.7151</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0044</v>
+        <v>0.0051</v>
       </c>
       <c r="BF3" t="n">
-        <v>238.2</v>
+        <v>248</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6106</v>
+        <v>6.892</v>
       </c>
       <c r="BH3" t="n">
-        <v>142</v>
+        <v>159.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.8477</v>
+        <v>4.7223</v>
       </c>
       <c r="BJ3" t="n">
-        <v>147.8</v>
+        <v>138</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6106</v>
+        <v>6.892</v>
       </c>
       <c r="BL3" t="n">
-        <v>516</v>
+        <v>498.6</v>
       </c>
       <c r="BM3" t="n">
-        <v>4.8477</v>
+        <v>4.7223</v>
       </c>
       <c r="BN3" t="n">
         <v>25</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.3855</v>
+        <v>0.3777</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.5633</v>
+        <v>0.5324</v>
       </c>
       <c r="BQ3" t="n">
         <v>0.5</v>
@@ -1546,19 +1546,19 @@
         <v>608</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6985</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.223</v>
+        <v>0.2627</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.6292</v>
+        <v>0.653</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.5052</v>
+        <v>0.5466</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.7533</v>
+        <v>0.7593</v>
       </c>
       <c r="CB3" t="n">
         <v>0.1908</v>
@@ -1567,19 +1567,19 @@
         <v>330</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.6221</v>
+        <v>0.6319</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1976</v>
+        <v>0.208</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.6052</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.7438</v>
+        <v>0.7462</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.4667</v>
+        <v>0.4765</v>
       </c>
       <c r="CI3" t="n">
         <v>0.7544999999999999</v>
@@ -1588,19 +1588,19 @@
         <v>106</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.7776</v>
+        <v>0.7607</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.3462</v>
+        <v>0.316</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.7089</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.7048</v>
+        <v>0.6762</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.7129</v>
+        <v>0.7059</v>
       </c>
       <c r="CP3" t="n">
         <v>0.1981</v>
@@ -1609,19 +1609,19 @@
         <v>464</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.766</v>
+        <v>0.7734</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.3882</v>
+        <v>0.4556</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.6924</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.5767</v>
+        <v>0.6014</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.8082</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="CW3" t="n">
         <v>0.3147</v>
@@ -1630,19 +1630,19 @@
         <v>607</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.7935</v>
+        <v>0.8027</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.4326</v>
+        <v>0.4922</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.7156</v>
+        <v>0.7448</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.6552</v>
+        <v>0.6767</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.776</v>
+        <v>0.8128</v>
       </c>
       <c r="DD3" t="n">
         <v>0.3822</v>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1700,176 +1700,176 @@
         <v>0.3697</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7611</v>
+        <v>0.7716</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0066</v>
+        <v>0.0067</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6814</v>
+        <v>0.7043</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0068</v>
+        <v>0.0062</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0673</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3052</v>
+        <v>0.2478</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6725</v>
+        <v>0.679</v>
       </c>
       <c r="T4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.4549</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.7086</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.6539</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.7632</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>보정</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>배포본(공통폴드.npz)</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.6186</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.0107</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.4327</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.0411</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.3728</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.6897</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.6503</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.7292</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>보정</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>배포본(공통폴드.npz)</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.0342</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.0288</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.5855</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0195</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.0258</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.0133</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>0.7</v>
+        <v>0.7228</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0137</v>
+        <v>0.0107</v>
       </c>
       <c r="AL4" t="n">
-        <v>251</v>
+        <v>252.4</v>
       </c>
       <c r="AM4" t="n">
-        <v>13.2098</v>
+        <v>8.2037</v>
       </c>
       <c r="AN4" t="n">
-        <v>178.2</v>
+        <v>155.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>18.9526</v>
+        <v>11.6276</v>
       </c>
       <c r="AP4" t="n">
-        <v>135</v>
+        <v>133.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.2098</v>
+        <v>8.2037</v>
       </c>
       <c r="AR4" t="n">
-        <v>479.8</v>
+        <v>502.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>18.9526</v>
+        <v>11.6276</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.5663</v>
+        <v>0.5979</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0072</v>
+        <v>0.0149</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.8167</v>
+        <v>0.8185</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0116</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6591</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0148</v>
+        <v>0.0141</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.3949</v>
+        <v>0.4258</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0154</v>
+        <v>0.0213</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.6915</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0067</v>
+        <v>0.0106</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.7241</v>
+        <v>0.737</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0076</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>218.6</v>
+        <v>230.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.7928</v>
+        <v>5.7619</v>
       </c>
       <c r="BH4" t="n">
-        <v>120.6</v>
+        <v>119.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>7.6026</v>
+        <v>5.1769</v>
       </c>
       <c r="BJ4" t="n">
-        <v>167.4</v>
+        <v>155.2</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.7928</v>
+        <v>5.7619</v>
       </c>
       <c r="BL4" t="n">
-        <v>537.4</v>
+        <v>538.6</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.6026</v>
+        <v>5.1769</v>
       </c>
       <c r="BN4" t="n">
         <v>25</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.3559</v>
+        <v>0.3911</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.5011</v>
+        <v>0.4972</v>
       </c>
       <c r="BQ4" t="n">
         <v>0.5</v>
@@ -1890,19 +1890,19 @@
         <v>608</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.6817</v>
+        <v>0.709</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.198</v>
+        <v>0.2438</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6347</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.4586</v>
+        <v>0.4707</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.7663</v>
+        <v>0.7988</v>
       </c>
       <c r="CB4" t="n">
         <v>0.1908</v>
@@ -1911,19 +1911,19 @@
         <v>330</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6883</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.2026</v>
+        <v>0.2587</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.609</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.739</v>
+        <v>0.7454</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.479</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="CI4" t="n">
         <v>0.7544999999999999</v>
@@ -1932,19 +1932,19 @@
         <v>106</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.7459</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.3484</v>
+        <v>0.3113</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.705</v>
+        <v>0.6775</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.6571</v>
+        <v>0.581</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.7529</v>
+        <v>0.7741</v>
       </c>
       <c r="CP4" t="n">
         <v>0.1981</v>
@@ -1953,19 +1953,19 @@
         <v>464</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.7561</v>
+        <v>0.787</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.3453</v>
+        <v>0.4305</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.6745</v>
+        <v>0.713</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.5685</v>
+        <v>0.5959</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.7805</v>
+        <v>0.8302</v>
       </c>
       <c r="CW4" t="n">
         <v>0.3147</v>
@@ -1974,19 +1974,19 @@
         <v>607</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.7835</v>
+        <v>0.8068</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.4027</v>
+        <v>0.4658</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.7033</v>
+        <v>0.7332</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.6595</v>
+        <v>0.675</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.7472</v>
+        <v>0.7915</v>
       </c>
       <c r="DD4" t="n">
         <v>0.3822</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2044,46 +2044,46 @@
         <v>0.3697</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7588</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0037</v>
+        <v>0.0044</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6911</v>
+        <v>0.6939</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0023</v>
+        <v>0.0046</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0677</v>
+        <v>0.0687</v>
       </c>
       <c r="R5" t="n">
         <v>0.2616</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6563</v>
+        <v>0.6543</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0105</v>
+        <v>0.0062</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4461</v>
+        <v>0.4525</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0466</v>
+        <v>0.0405</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4072</v>
+        <v>0.4065</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7036</v>
+        <v>0.7039</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.629</v>
+        <v>0.6337</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7781</v>
+        <v>0.7742</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -2099,121 +2099,121 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>0.0263</v>
+        <v>0.0175</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0302</v>
+        <v>0.0152</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6258</v>
+        <v>0.6224</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0236</v>
+        <v>0.0098</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0173</v>
+        <v>0.0053</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0072</v>
+        <v>0.0029</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.723</v>
+        <v>0.7222</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0115</v>
+        <v>0.004</v>
       </c>
       <c r="AL5" t="n">
-        <v>242.8</v>
+        <v>244.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>10.1587</v>
+        <v>6.7676</v>
       </c>
       <c r="AN5" t="n">
-        <v>146</v>
+        <v>148.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>19.8746</v>
+        <v>10.015</v>
       </c>
       <c r="AP5" t="n">
-        <v>143.2</v>
+        <v>141.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.1587</v>
+        <v>6.7676</v>
       </c>
       <c r="AR5" t="n">
-        <v>512</v>
+        <v>509.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.8746</v>
+        <v>10.015</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.5788</v>
+        <v>0.5927</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0166</v>
+        <v>0.0163</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.8283</v>
+        <v>0.8195</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.6641</v>
+        <v>0.6583</v>
       </c>
       <c r="AY5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.7060999999999999</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.7356</v>
+      </c>
+      <c r="BE5" t="n">
         <v>0.0035</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>0.4205</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.0109</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.7035</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.0066</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.0041</v>
-      </c>
       <c r="BF5" t="n">
-        <v>223.4</v>
+        <v>228.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4265</v>
+        <v>6.3008</v>
       </c>
       <c r="BH5" t="n">
-        <v>113</v>
+        <v>118.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.9155</v>
+        <v>3.9623</v>
       </c>
       <c r="BJ5" t="n">
-        <v>162.6</v>
+        <v>157.2</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4265</v>
+        <v>6.3008</v>
       </c>
       <c r="BL5" t="n">
-        <v>545</v>
+        <v>539.2</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.9155</v>
+        <v>3.9623</v>
       </c>
       <c r="BN5" t="n">
         <v>25</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.3665</v>
+        <v>0.3812</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.5354</v>
+        <v>0.5346</v>
       </c>
       <c r="BQ5" t="n">
         <v>0.5</v>
@@ -2234,19 +2234,19 @@
         <v>608</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7195</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.2954</v>
+        <v>0.292</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.6549</v>
+        <v>0.6553</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.4707</v>
+        <v>0.4776</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.839</v>
+        <v>0.8329</v>
       </c>
       <c r="CB5" t="n">
         <v>0.1908</v>
@@ -2255,19 +2255,19 @@
         <v>330</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.6086</v>
+        <v>0.6123</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1083</v>
+        <v>0.1024</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.5593</v>
+        <v>0.556</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.694</v>
+        <v>0.6972</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.4247</v>
+        <v>0.4148</v>
       </c>
       <c r="CI5" t="n">
         <v>0.7544999999999999</v>
@@ -2276,19 +2276,19 @@
         <v>106</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.7873</v>
+        <v>0.7987</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.4195</v>
+        <v>0.4415</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.7478</v>
+        <v>0.7597</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.7333</v>
+        <v>0.7429</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.7624</v>
+        <v>0.7765</v>
       </c>
       <c r="CP5" t="n">
         <v>0.1981</v>
@@ -2297,19 +2297,19 @@
         <v>464</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.7736</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.4209</v>
+        <v>0.4092</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.7043</v>
+        <v>0.6969</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.5658</v>
+        <v>0.5466</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.8428</v>
+        <v>0.8472</v>
       </c>
       <c r="CW5" t="n">
         <v>0.3147</v>
@@ -2318,19 +2318,19 @@
         <v>607</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.7821</v>
+        <v>0.7914</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.4484</v>
+        <v>0.4498</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.7175</v>
+        <v>0.7194</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.6052</v>
+        <v>0.6138</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.8299</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="DD5" t="n">
         <v>0.3822</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2388,176 +2388,176 @@
         <v>0.3697</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7657</v>
+        <v>0.7701</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0051</v>
+        <v>0.0062</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6962</v>
+        <v>0.7007</v>
       </c>
       <c r="P6" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.6301</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>보정</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>배포본(공통폴드.npz)</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.6379</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.7308</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>243.2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>6.0166</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10.2567</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6.0166</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>519.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>10.2567</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.8438</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.6792</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="BA6" t="n">
         <v>0.0083</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.06950000000000001</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.2616</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.6822</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.4374</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.0384</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.4158</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.7068</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.6228</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.7909</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>보정</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>배포본(공통폴드.npz)</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.6365</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.7287</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>240.4</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>5.1769</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>137.6</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>11.6319</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>145.6</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.1769</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>520.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11.6319</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.5611</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.8416</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.6752</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.4214</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.0121</v>
-      </c>
       <c r="BB6" t="n">
-        <v>0.7014</v>
+        <v>0.7037</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0064</v>
+        <v>0.0044</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.7379</v>
+        <v>0.7402</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0051</v>
+        <v>0.0035</v>
       </c>
       <c r="BF6" t="n">
-        <v>216.6</v>
+        <v>217.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.0299</v>
+        <v>3.6469</v>
       </c>
       <c r="BH6" t="n">
-        <v>104.2</v>
+        <v>102.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.2711</v>
+        <v>3.0332</v>
       </c>
       <c r="BJ6" t="n">
-        <v>169.4</v>
+        <v>168.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.0299</v>
+        <v>3.6469</v>
       </c>
       <c r="BL6" t="n">
-        <v>553.8</v>
+        <v>555.2</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.2711</v>
+        <v>3.0332</v>
       </c>
       <c r="BN6" t="n">
         <v>25</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.3649</v>
+        <v>0.3772</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.5108</v>
+        <v>0.5205</v>
       </c>
       <c r="BQ6" t="n">
         <v>0.5</v>
@@ -2578,19 +2578,19 @@
         <v>608</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.7146</v>
+        <v>0.7194</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.3014</v>
+        <v>0.3157</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6657</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.4724</v>
+        <v>0.4862</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.8431</v>
+        <v>0.8451</v>
       </c>
       <c r="CB6" t="n">
         <v>0.1908</v>
@@ -2599,19 +2599,19 @@
         <v>330</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.6349</v>
+        <v>0.6385</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1302</v>
+        <v>0.1154</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.5722</v>
+        <v>0.5635</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.6851</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.4593</v>
+        <v>0.437</v>
       </c>
       <c r="CI6" t="n">
         <v>0.7544999999999999</v>
@@ -2620,19 +2620,19 @@
         <v>106</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.7993</v>
+        <v>0.8052</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.4522</v>
+        <v>0.4555</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.7595</v>
+        <v>0.7607</v>
       </c>
       <c r="CN6" t="n">
         <v>0.7143</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.8047</v>
+        <v>0.8071</v>
       </c>
       <c r="CP6" t="n">
         <v>0.1981</v>
@@ -2641,19 +2641,19 @@
         <v>464</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.7724</v>
+        <v>0.7721</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.4312</v>
+        <v>0.4304</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.7083</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.5658</v>
+        <v>0.5603</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.8509</v>
+        <v>0.8541</v>
       </c>
       <c r="CW6" t="n">
         <v>0.3147</v>
@@ -2662,19 +2662,19 @@
         <v>607</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.7793</v>
+        <v>0.788</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.4569</v>
+        <v>0.461</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.7218</v>
+        <v>0.7237</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.6095</v>
+        <v>0.6112</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.8341</v>
+        <v>0.8363</v>
       </c>
       <c r="DD6" t="n">
         <v>0.3822</v>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2732,46 +2732,46 @@
         <v>0.3697</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7028</v>
+        <v>0.6968</v>
       </c>
       <c r="N7" t="n">
-        <v>0.004</v>
+        <v>0.0035</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6364</v>
+        <v>0.6505</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0077</v>
+        <v>0.002</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0664</v>
+        <v>0.0463</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3274</v>
+        <v>0.2353</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6092</v>
+        <v>0.6026</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0095</v>
+        <v>0.0076</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5224</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0451</v>
+        <v>0.0357</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3087</v>
+        <v>0.2823</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6535</v>
+        <v>0.6429</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5767</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.7489</v>
+        <v>0.7091</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2787,121 +2787,121 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>0.0428</v>
+        <v>0.0215</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0355</v>
+        <v>0.0229</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5673</v>
+        <v>0.5381</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0181</v>
+        <v>0.0124</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0102</v>
+        <v>0.0137</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.006</v>
+        <v>0.0067</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.6784</v>
+        <v>0.6602</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.008</v>
+        <v>0.0091</v>
       </c>
       <c r="AL7" t="n">
-        <v>215.4</v>
+        <v>222.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>16.5318</v>
+        <v>8.294600000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>165.2</v>
+        <v>191.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>23.3495</v>
+        <v>15.0599</v>
       </c>
       <c r="AP7" t="n">
-        <v>170.6</v>
+        <v>163.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.5318</v>
+        <v>8.294600000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>492.8</v>
+        <v>466.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>23.3495</v>
+        <v>15.0599</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.5803</v>
+        <v>0.5819</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0192</v>
+        <v>0.0054</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.7392</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0216</v>
+        <v>0.0054</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.5668</v>
+        <v>0.5417</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0148</v>
+        <v>0.0052</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3182</v>
+        <v>0.2892</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0138</v>
+        <v>0.0076</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6466</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0062</v>
+        <v>0.0038</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.6805</v>
+        <v>0.6634</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0039</v>
       </c>
       <c r="BF7" t="n">
-        <v>224</v>
+        <v>224.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4162</v>
+        <v>2.0736</v>
       </c>
       <c r="BH7" t="n">
-        <v>171.6</v>
+        <v>190</v>
       </c>
       <c r="BI7" t="n">
-        <v>14.2232</v>
+        <v>3.5355</v>
       </c>
       <c r="BJ7" t="n">
-        <v>162</v>
+        <v>161.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4162</v>
+        <v>2.0736</v>
       </c>
       <c r="BL7" t="n">
-        <v>486.4</v>
+        <v>468</v>
       </c>
       <c r="BM7" t="n">
-        <v>14.2232</v>
+        <v>3.5355</v>
       </c>
       <c r="BN7" t="n">
         <v>25</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.4312</v>
+        <v>0.4146</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.6202</v>
+        <v>0.6172</v>
       </c>
       <c r="BQ7" t="n">
         <v>0.5</v>
@@ -2922,19 +2922,19 @@
         <v>608</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.6378</v>
+        <v>0.6631</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.1892</v>
+        <v>0.1986</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.6045</v>
+        <v>0.6157</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.4224</v>
+        <v>0.4879</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.7866</v>
+        <v>0.7435</v>
       </c>
       <c r="CB7" t="n">
         <v>0.1908</v>
@@ -2943,19 +2943,19 @@
         <v>330</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.6273</v>
+        <v>0.6141</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1071</v>
+        <v>0.1277</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5729</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.6233</v>
+        <v>0.6249</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.4988</v>
+        <v>0.521</v>
       </c>
       <c r="CI7" t="n">
         <v>0.7544999999999999</v>
@@ -2964,19 +2964,19 @@
         <v>106</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6575</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.2661</v>
+        <v>0.1543</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.6514</v>
+        <v>0.5923</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.5333</v>
+        <v>0.4952</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.7694</v>
+        <v>0.6894</v>
       </c>
       <c r="CP7" t="n">
         <v>0.1981</v>
@@ -2985,19 +2985,19 @@
         <v>464</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.6496</v>
+        <v>0.6932</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.2424</v>
+        <v>0.3234</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.6085</v>
+        <v>0.6499</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.3767</v>
+        <v>0.4521</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.8403</v>
+        <v>0.8478</v>
       </c>
       <c r="CW7" t="n">
         <v>0.3147</v>
@@ -3006,19 +3006,19 @@
         <v>607</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.6972</v>
+        <v>0.7345</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.3155</v>
+        <v>0.3832</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.6486</v>
+        <v>0.6859</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.4897</v>
+        <v>0.5638</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.8075</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="DD7" t="n">
         <v>0.3822</v>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3076,46 +3076,46 @@
         <v>0.6830000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6069</v>
+        <v>0.6082</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0129</v>
+        <v>0.0075</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5823</v>
+        <v>0.584</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0116</v>
+        <v>0.0061</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0246</v>
+        <v>0.0242</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2301</v>
+        <v>0.2237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.774</v>
+        <v>0.7734</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0105</v>
+        <v>0.0058</v>
       </c>
       <c r="U8" t="n">
-        <v>0.595</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1018</v>
+        <v>0.0946</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1215</v>
+        <v>0.1201</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5645</v>
+        <v>0.5618</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5694</v>
+        <v>0.4154</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5595</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -3131,121 +3131,121 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>0.0776</v>
+        <v>0.0785</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0844</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.7371</v>
+        <v>0.7565</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.017</v>
+        <v>0.0269</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0302</v>
+        <v>0.0389</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0158</v>
+        <v>0.0202</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.5663</v>
+        <v>0.5082</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0298</v>
+        <v>0.0327</v>
       </c>
       <c r="AL8" t="n">
-        <v>406</v>
+        <v>296.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>55.3579</v>
+        <v>55.9661</v>
       </c>
       <c r="AN8" t="n">
-        <v>145.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>28.1372</v>
+        <v>27.9428</v>
       </c>
       <c r="AP8" t="n">
-        <v>307</v>
+        <v>416.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>55.3579</v>
+        <v>55.9661</v>
       </c>
       <c r="AR8" t="n">
-        <v>185.2</v>
+        <v>234.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>28.1372</v>
+        <v>27.9428</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.7425</v>
+        <v>0.7091</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0198</v>
+        <v>0.0183</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.4097</v>
+        <v>0.4169</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0253</v>
+        <v>0.0301</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.7305</v>
+        <v>0.7238</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.006</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.1538</v>
+        <v>0.1247</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0181</v>
+        <v>0.0232</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0091</v>
+        <v>0.0121</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.637</v>
+        <v>0.6165</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0097</v>
+        <v>0.0103</v>
       </c>
       <c r="BF8" t="n">
-        <v>529.4</v>
+        <v>505.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>14.1174</v>
+        <v>13.0499</v>
       </c>
       <c r="BH8" t="n">
-        <v>195.4</v>
+        <v>193</v>
       </c>
       <c r="BI8" t="n">
-        <v>8.384499999999999</v>
+        <v>9.9499</v>
       </c>
       <c r="BJ8" t="n">
-        <v>183.6</v>
+        <v>207.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>14.1174</v>
+        <v>13.0499</v>
       </c>
       <c r="BL8" t="n">
-        <v>135.6</v>
+        <v>138</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.384499999999999</v>
+        <v>9.9499</v>
       </c>
       <c r="BN8" t="n">
         <v>25</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.4788</v>
+        <v>0.502</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.7926</v>
+        <v>0.8622</v>
       </c>
       <c r="BQ8" t="n">
         <v>0.5</v>
@@ -3266,19 +3266,19 @@
         <v>608</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.5587</v>
+        <v>0.5577</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0578</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.5296</v>
+        <v>0.5341</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.5344</v>
+        <v>0.3949</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.5248</v>
+        <v>0.6734</v>
       </c>
       <c r="CB8" t="n">
         <v>0.6414</v>
@@ -3287,19 +3287,19 @@
         <v>330</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.7668</v>
+        <v>0.7897</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.2528</v>
+        <v>0.214</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.6199</v>
+        <v>0.4486</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.7684</v>
+        <v>0.8789</v>
       </c>
       <c r="CI8" t="n">
         <v>0.8848</v>
@@ -3308,19 +3308,19 @@
         <v>106</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.5642</v>
+        <v>0.5631</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0829</v>
+        <v>0.0854</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.5451</v>
+        <v>0.542</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.5355</v>
+        <v>0.3613</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.5547</v>
+        <v>0.7227</v>
       </c>
       <c r="CP8" t="n">
         <v>0.2925</v>
@@ -3329,19 +3329,19 @@
         <v>464</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.6334</v>
+        <v>0.6347</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.1567</v>
+        <v>0.1933</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.5815</v>
+        <v>0.5997</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.5828</v>
+        <v>0.4838</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.7155</v>
       </c>
       <c r="CW8" t="n">
         <v>0.653</v>
@@ -3350,19 +3350,19 @@
         <v>607</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.6652</v>
+        <v>0.6657</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.1929</v>
+        <v>0.2122</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.6027</v>
+        <v>0.6151</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.654</v>
+        <v>0.5474</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.5514</v>
+        <v>0.6829</v>
       </c>
       <c r="DD8" t="n">
         <v>0.7018</v>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3420,46 +3420,46 @@
         <v>0.6830000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6069</v>
+        <v>0.6082</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0129</v>
+        <v>0.0075</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5823</v>
+        <v>0.584</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0116</v>
+        <v>0.0061</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0246</v>
+        <v>0.0242</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2301</v>
+        <v>0.2237</v>
       </c>
       <c r="S9" t="n">
-        <v>0.774</v>
+        <v>0.7734</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0105</v>
+        <v>0.0058</v>
       </c>
       <c r="U9" t="n">
-        <v>0.595</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1018</v>
+        <v>0.0946</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1215</v>
+        <v>0.1201</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5645</v>
+        <v>0.5618</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5694</v>
+        <v>0.4154</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5595</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -3475,121 +3475,121 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>0.0776</v>
+        <v>0.0785</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0844</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.7371</v>
+        <v>0.7565</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.017</v>
+        <v>0.0269</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0302</v>
+        <v>0.0389</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0158</v>
+        <v>0.0202</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5663</v>
+        <v>0.5082</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0298</v>
+        <v>0.0327</v>
       </c>
       <c r="AL9" t="n">
-        <v>406</v>
+        <v>296.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>55.3579</v>
+        <v>55.9661</v>
       </c>
       <c r="AN9" t="n">
-        <v>145.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AO9" t="n">
-        <v>28.1372</v>
+        <v>27.9428</v>
       </c>
       <c r="AP9" t="n">
-        <v>307</v>
+        <v>416.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>55.3579</v>
+        <v>55.9661</v>
       </c>
       <c r="AR9" t="n">
-        <v>185.2</v>
+        <v>234.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>28.1372</v>
+        <v>27.9428</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.7425</v>
+        <v>0.7091</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0198</v>
+        <v>0.0183</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.4097</v>
+        <v>0.4169</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0253</v>
+        <v>0.0301</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.7305</v>
+        <v>0.7238</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.006</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1538</v>
+        <v>0.1247</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0181</v>
+        <v>0.0232</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0091</v>
+        <v>0.0121</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.637</v>
+        <v>0.6165</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0097</v>
+        <v>0.0103</v>
       </c>
       <c r="BF9" t="n">
-        <v>529.4</v>
+        <v>505.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>14.1174</v>
+        <v>13.0499</v>
       </c>
       <c r="BH9" t="n">
-        <v>195.4</v>
+        <v>193</v>
       </c>
       <c r="BI9" t="n">
-        <v>8.384499999999999</v>
+        <v>9.9499</v>
       </c>
       <c r="BJ9" t="n">
-        <v>183.6</v>
+        <v>207.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>14.1174</v>
+        <v>13.0499</v>
       </c>
       <c r="BL9" t="n">
-        <v>135.6</v>
+        <v>138</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.384499999999999</v>
+        <v>9.9499</v>
       </c>
       <c r="BN9" t="n">
         <v>25</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.4788</v>
+        <v>0.502</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.7926</v>
+        <v>0.8622</v>
       </c>
       <c r="BQ9" t="n">
         <v>0.5</v>
@@ -3610,19 +3610,19 @@
         <v>608</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.5587</v>
+        <v>0.5577</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0578</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.5296</v>
+        <v>0.5341</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.5344</v>
+        <v>0.3949</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.5248</v>
+        <v>0.6734</v>
       </c>
       <c r="CB9" t="n">
         <v>0.6414</v>
@@ -3631,19 +3631,19 @@
         <v>330</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.7668</v>
+        <v>0.7897</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.2528</v>
+        <v>0.214</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.6199</v>
+        <v>0.4486</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.7684</v>
+        <v>0.8789</v>
       </c>
       <c r="CI9" t="n">
         <v>0.8848</v>
@@ -3652,19 +3652,19 @@
         <v>106</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.5642</v>
+        <v>0.5631</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0829</v>
+        <v>0.0854</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.5451</v>
+        <v>0.542</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.5355</v>
+        <v>0.3613</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.5547</v>
+        <v>0.7227</v>
       </c>
       <c r="CP9" t="n">
         <v>0.2925</v>
@@ -3673,19 +3673,19 @@
         <v>464</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.6334</v>
+        <v>0.6347</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.1567</v>
+        <v>0.1933</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.5815</v>
+        <v>0.5997</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.5828</v>
+        <v>0.4838</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.7155</v>
       </c>
       <c r="CW9" t="n">
         <v>0.653</v>
@@ -3694,19 +3694,19 @@
         <v>607</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.6652</v>
+        <v>0.6657</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.1929</v>
+        <v>0.2122</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.6027</v>
+        <v>0.6151</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.654</v>
+        <v>0.5474</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.5514</v>
+        <v>0.6829</v>
       </c>
       <c r="DD9" t="n">
         <v>0.7018</v>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3764,46 +3764,46 @@
         <v>0.3362</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7015</v>
+        <v>0.7018</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0023</v>
+        <v>0.0033</v>
       </c>
       <c r="O10" t="n">
-        <v>0.647</v>
+        <v>0.641</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0034</v>
+        <v>0.0067</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0545</v>
+        <v>0.0608</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2705</v>
+        <v>0.3013</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5241</v>
+        <v>0.5285</v>
       </c>
       <c r="T10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4455</v>
+        <v>0.4412</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0677</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2797</v>
+        <v>0.2748</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6465</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6287</v>
+        <v>0.6466</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6643</v>
+        <v>0.6427</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -3819,121 +3819,121 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>0.0338</v>
+        <v>0.0328</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.4874</v>
+        <v>0.4785</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0128</v>
+        <v>0.0091</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0091</v>
+        <v>0.0134</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0045</v>
+        <v>0.0073</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.6523</v>
+        <v>0.644</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0114</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>223.8</v>
+        <v>230.2</v>
       </c>
       <c r="AM10" t="n">
-        <v>12.0499</v>
+        <v>11.6919</v>
       </c>
       <c r="AN10" t="n">
-        <v>236</v>
+        <v>251.2</v>
       </c>
       <c r="AO10" t="n">
-        <v>23.2056</v>
+        <v>18.2538</v>
       </c>
       <c r="AP10" t="n">
-        <v>132.2</v>
+        <v>125.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.0499</v>
+        <v>11.6919</v>
       </c>
       <c r="AR10" t="n">
-        <v>467</v>
+        <v>451.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>23.2056</v>
+        <v>18.2538</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5775</v>
+        <v>0.5904</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.7275</v>
+        <v>0.7101</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0103</v>
+        <v>0.007</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.5178</v>
+        <v>0.5077</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0102</v>
+        <v>0.0076</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2976</v>
+        <v>0.291</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0132</v>
+        <v>0.0127</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.6525</v>
+        <v>0.6503</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0064</v>
+        <v>0.0066</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.6771</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0076</v>
+        <v>0.006</v>
       </c>
       <c r="BF10" t="n">
-        <v>205.6</v>
+        <v>210.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.5166</v>
+        <v>3.9623</v>
       </c>
       <c r="BH10" t="n">
-        <v>191.6</v>
+        <v>203.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>7.2319</v>
+        <v>4.9193</v>
       </c>
       <c r="BJ10" t="n">
-        <v>150.4</v>
+        <v>145.8</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.5166</v>
+        <v>3.9623</v>
       </c>
       <c r="BL10" t="n">
-        <v>511.4</v>
+        <v>499.2</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.2319</v>
+        <v>4.9193</v>
       </c>
       <c r="BN10" t="n">
         <v>25</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.3324</v>
+        <v>0.311</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.5815</v>
+        <v>0.578</v>
       </c>
       <c r="BQ10" t="n">
         <v>0.5</v>
@@ -3954,19 +3954,19 @@
         <v>544</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.653</v>
+        <v>0.6279</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.1403</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.5819</v>
+        <v>0.5567</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.422</v>
+        <v>0.404</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.7419</v>
+        <v>0.7095</v>
       </c>
       <c r="CB10" t="n">
         <v>0.1838</v>
@@ -3975,19 +3975,19 @@
         <v>421</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.6411</v>
+        <v>0.6552</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.2109</v>
+        <v>0.2446</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.6028</v>
+        <v>0.6175</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.7174</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.4883</v>
+        <v>0.4804</v>
       </c>
       <c r="CI10" t="n">
         <v>0.5748</v>
@@ -3996,19 +3996,19 @@
         <v>94</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.6377</v>
+        <v>0.6109</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.146</v>
+        <v>0.1104</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.5995</v>
+        <v>0.5746</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.5714</v>
+        <v>0.5143</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.635</v>
       </c>
       <c r="CP10" t="n">
         <v>0.1489</v>
@@ -4017,19 +4017,19 @@
         <v>461</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.6992</v>
+        <v>0.7166</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.244</v>
+        <v>0.2854</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.6259</v>
+        <v>0.6485</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.5174</v>
+        <v>0.5609</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7362</v>
       </c>
       <c r="CW10" t="n">
         <v>0.2993</v>
@@ -4038,19 +4038,19 @@
         <v>552</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.7191</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.275</v>
+        <v>0.3027</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.6408</v>
+        <v>0.6561</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.578</v>
+        <v>0.6136</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.7036</v>
+        <v>0.6986</v>
       </c>
       <c r="DD10" t="n">
         <v>0.346</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -4108,46 +4108,46 @@
         <v>0.3362</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7301</v>
+        <v>0.7379</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004</v>
+        <v>0.0041</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6604</v>
+        <v>0.6655</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0052</v>
+        <v>0.0063</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0697</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3029</v>
+        <v>0.3043</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5594</v>
+        <v>0.5723</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0052</v>
+        <v>0.0117</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4047</v>
+        <v>0.4294</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0497</v>
+        <v>0.0638</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3193</v>
+        <v>0.3191</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6682</v>
+        <v>0.6676</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.6837</v>
+        <v>0.6657</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.6526</v>
+        <v>0.6694</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4163,121 +4163,121 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>0.0374</v>
+        <v>0.0289</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0303</v>
+        <v>0.0266</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4996</v>
+        <v>0.5054</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0111</v>
+        <v>0.0105</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0161</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0048</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.6631</v>
+        <v>0.6682</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0108</v>
+        <v>0.0091</v>
       </c>
       <c r="AL11" t="n">
-        <v>243.4</v>
+        <v>237</v>
       </c>
       <c r="AM11" t="n">
-        <v>13.2966</v>
+        <v>10.2713</v>
       </c>
       <c r="AN11" t="n">
-        <v>244.2</v>
+        <v>232.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>21.3237</v>
+        <v>18.7297</v>
       </c>
       <c r="AP11" t="n">
-        <v>112.6</v>
+        <v>119</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.2966</v>
+        <v>10.2713</v>
       </c>
       <c r="AR11" t="n">
-        <v>458.8</v>
+        <v>470.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>21.3237</v>
+        <v>18.7297</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.5742</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0287</v>
+        <v>0.0129</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.7494</v>
+        <v>0.7474</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0102</v>
+        <v>0.0057</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.537</v>
+        <v>0.5453</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0056</v>
+        <v>0.0048</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.3185</v>
+        <v>0.3385</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0171</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6728</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0101</v>
+        <v>0.0052</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.6905</v>
+        <v>0.6973</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0048</v>
+        <v>0.0036</v>
       </c>
       <c r="BF11" t="n">
-        <v>204.4</v>
+        <v>213</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.2127</v>
+        <v>4.5826</v>
       </c>
       <c r="BH11" t="n">
-        <v>176.2</v>
+        <v>177.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>7.1554</v>
+        <v>4.0373</v>
       </c>
       <c r="BJ11" t="n">
-        <v>151.6</v>
+        <v>143</v>
       </c>
       <c r="BK11" t="n">
-        <v>10.2127</v>
+        <v>4.5826</v>
       </c>
       <c r="BL11" t="n">
-        <v>526.8</v>
+        <v>525.4</v>
       </c>
       <c r="BM11" t="n">
-        <v>7.1554</v>
+        <v>4.0373</v>
       </c>
       <c r="BN11" t="n">
         <v>25</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.3017</v>
+        <v>0.3203</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.5317</v>
+        <v>0.5392</v>
       </c>
       <c r="BQ11" t="n">
         <v>0.5</v>
@@ -4298,19 +4298,19 @@
         <v>544</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.6986</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.2092</v>
+        <v>0.1908</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.623</v>
+        <v>0.6092</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.496</v>
+        <v>0.45</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.75</v>
+        <v>0.7685</v>
       </c>
       <c r="CB11" t="n">
         <v>0.1838</v>
@@ -4319,19 +4319,19 @@
         <v>421</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.6193</v>
+        <v>0.6299</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.1908</v>
+        <v>0.1893</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.5895</v>
+        <v>0.5888</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.7612</v>
+        <v>0.7587</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.4179</v>
+        <v>0.419</v>
       </c>
       <c r="CI11" t="n">
         <v>0.5748</v>
@@ -4340,19 +4340,19 @@
         <v>94</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.732</v>
+        <v>0.7457</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.2339</v>
+        <v>0.2075</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.6616</v>
+        <v>0.64</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.6857</v>
+        <v>0.6</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.6375</v>
+        <v>0.68</v>
       </c>
       <c r="CP11" t="n">
         <v>0.1489</v>
@@ -4361,19 +4361,19 @@
         <v>461</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.7386</v>
+        <v>0.7519</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.3138</v>
+        <v>0.33</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.6623</v>
+        <v>0.6687</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.5754</v>
+        <v>0.5652</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.7492</v>
+        <v>0.7721</v>
       </c>
       <c r="CW11" t="n">
         <v>0.2993</v>
@@ -4382,19 +4382,19 @@
         <v>552</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.7489</v>
+        <v>0.7658</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.3491</v>
+        <v>0.3535</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.68</v>
+        <v>0.6803</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.6503</v>
+        <v>0.6209</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.7097</v>
+        <v>0.7396</v>
       </c>
       <c r="DD11" t="n">
         <v>0.346</v>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -4452,46 +4452,46 @@
         <v>0.3362</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7556</v>
+        <v>0.7599</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0071</v>
+        <v>0.005</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7</v>
+        <v>0.7038</v>
       </c>
       <c r="P12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0556</v>
+        <v>0.0561</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2175</v>
+        <v>0.2159</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6292</v>
+        <v>0.6411</v>
       </c>
       <c r="T12" t="n">
-        <v>0.012</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4011</v>
+        <v>0.4126</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0459</v>
+        <v>0.0545</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3587</v>
+        <v>0.3562</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6863</v>
+        <v>0.6837</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6539</v>
+        <v>0.6343</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.7186</v>
+        <v>0.7331</v>
       </c>
       <c r="AA12" t="n">
         <v>1</v>
@@ -4507,121 +4507,121 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>0.026</v>
+        <v>0.0177</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0235</v>
+        <v>0.0254</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.5411</v>
+        <v>0.547</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0126</v>
+        <v>0.0183</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0114</v>
+        <v>0.0175</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.006</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.6969</v>
+        <v>0.6999</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0127</v>
       </c>
       <c r="AL12" t="n">
-        <v>232.8</v>
+        <v>225.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>9.257400000000001</v>
+        <v>6.3008</v>
       </c>
       <c r="AN12" t="n">
-        <v>197.8</v>
+        <v>187.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>16.5439</v>
+        <v>17.841</v>
       </c>
       <c r="AP12" t="n">
-        <v>123.2</v>
+        <v>130.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.257400000000001</v>
+        <v>6.3008</v>
       </c>
       <c r="AR12" t="n">
-        <v>505.2</v>
+        <v>515.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>16.5439</v>
+        <v>17.841</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.5253</v>
+        <v>0.5371</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0158</v>
+        <v>0.0132</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.8242</v>
+        <v>0.829</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.6022</v>
+        <v>0.614</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0151</v>
+        <v>0.0074</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.3627</v>
+        <v>0.3796</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0191</v>
+        <v>0.0109</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.6747</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.7237</v>
+        <v>0.7309</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0083</v>
+        <v>0.0044</v>
       </c>
       <c r="BF12" t="n">
-        <v>187</v>
+        <v>191.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.6125</v>
+        <v>4.7117</v>
       </c>
       <c r="BH12" t="n">
-        <v>123.6</v>
+        <v>120.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>6.7305</v>
+        <v>4.0866</v>
       </c>
       <c r="BJ12" t="n">
-        <v>169</v>
+        <v>164.8</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6125</v>
+        <v>4.7117</v>
       </c>
       <c r="BL12" t="n">
-        <v>579.4</v>
+        <v>582.8</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.7305</v>
+        <v>4.0866</v>
       </c>
       <c r="BN12" t="n">
         <v>25</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.324</v>
+        <v>0.3036</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.4819</v>
+        <v>0.5172</v>
       </c>
       <c r="BQ12" t="n">
         <v>0.5</v>
@@ -4642,19 +4642,19 @@
         <v>544</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.6932</v>
+        <v>0.6904</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.2329</v>
+        <v>0.215</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.6327</v>
+        <v>0.6185</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.482</v>
+        <v>0.436</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.7833</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="CB12" t="n">
         <v>0.1838</v>
@@ -4663,19 +4663,19 @@
         <v>421</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.7053</v>
+        <v>0.7153</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.2877</v>
+        <v>0.2769</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.6425</v>
+        <v>0.6372</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.7207</v>
+        <v>0.7157</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.5642</v>
+        <v>0.5587</v>
       </c>
       <c r="CI12" t="n">
         <v>0.5748</v>
@@ -4684,19 +4684,19 @@
         <v>94</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.7642</v>
+        <v>0.7926</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.3225</v>
+        <v>0.3011</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.7168</v>
+        <v>0.6952</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.7286</v>
+        <v>0.6429</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.705</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="CP12" t="n">
         <v>0.1489</v>
@@ -4705,19 +4705,19 @@
         <v>461</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.7568</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.3601</v>
+        <v>0.3812</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.6862</v>
+        <v>0.6952</v>
       </c>
       <c r="CU12" t="n">
         <v>0.6014</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.7709</v>
+        <v>0.7889</v>
       </c>
       <c r="CW12" t="n">
         <v>0.2993</v>
@@ -4726,19 +4726,19 @@
         <v>552</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.7653</v>
+        <v>0.7748</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.3764</v>
+        <v>0.3858</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.6933</v>
+        <v>0.6973</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.6482</v>
+        <v>0.6461</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.7385</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="DD12" t="n">
         <v>0.346</v>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -4796,46 +4796,46 @@
         <v>0.3362</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7559</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0033</v>
+        <v>0.0026</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6813</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0732</v>
       </c>
       <c r="R13" t="n">
-        <v>0.281</v>
+        <v>0.2876</v>
       </c>
       <c r="S13" t="n">
-        <v>0.611</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3812</v>
+        <v>0.3884</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0486</v>
+        <v>0.0505</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3415</v>
+        <v>0.3557</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6858</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6708</v>
+        <v>0.6691</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.6871</v>
+        <v>0.7024</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -4851,121 +4851,121 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>0.0244</v>
+        <v>0.0211</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0262</v>
+        <v>0.0269</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.521</v>
+        <v>0.5331</v>
       </c>
       <c r="AG13" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.6912</v>
+      </c>
+      <c r="AK13" t="n">
         <v>0.0131</v>
       </c>
-      <c r="AH13" t="n">
-        <v>0.0116</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.6816</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.0106</v>
-      </c>
       <c r="AL13" t="n">
-        <v>238.8</v>
+        <v>238.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>8.7006</v>
+        <v>7.4967</v>
       </c>
       <c r="AN13" t="n">
-        <v>220</v>
+        <v>209.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>18.3984</v>
+        <v>18.8997</v>
       </c>
       <c r="AP13" t="n">
-        <v>117.2</v>
+        <v>117.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.7006</v>
+        <v>7.4967</v>
       </c>
       <c r="AR13" t="n">
-        <v>483</v>
+        <v>493.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>18.3984</v>
+        <v>18.8997</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.5478</v>
+        <v>0.5601</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0114</v>
+        <v>0.013</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.8065</v>
+        <v>0.8083</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0161</v>
+        <v>0.0117</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.5897</v>
+        <v>0.5969</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.017</v>
+        <v>0.0107</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.3613</v>
+        <v>0.3746</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0138</v>
+        <v>0.0089</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.6771</v>
+        <v>0.6842</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0052</v>
+        <v>0.0041</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.7195</v>
+        <v>0.7248</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="BF13" t="n">
-        <v>195</v>
+        <v>199.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.062</v>
+        <v>4.6152</v>
       </c>
       <c r="BH13" t="n">
-        <v>136</v>
+        <v>134.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>11.3358</v>
+        <v>8.1976</v>
       </c>
       <c r="BJ13" t="n">
-        <v>161</v>
+        <v>156.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.062</v>
+        <v>4.6152</v>
       </c>
       <c r="BL13" t="n">
-        <v>567</v>
+        <v>568.2</v>
       </c>
       <c r="BM13" t="n">
-        <v>11.3358</v>
+        <v>8.1976</v>
       </c>
       <c r="BN13" t="n">
         <v>25</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.3024</v>
+        <v>0.3078</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.4786</v>
+        <v>0.519</v>
       </c>
       <c r="BQ13" t="n">
         <v>0.5</v>
@@ -4986,19 +4986,19 @@
         <v>544</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.6942</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.1897</v>
+        <v>0.1953</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.6079</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.442</v>
+        <v>0.424</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.7739</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="CB13" t="n">
         <v>0.1838</v>
@@ -5007,19 +5007,19 @@
         <v>421</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.6612</v>
+        <v>0.6657</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.2385</v>
+        <v>0.2484</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.6181</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.7653</v>
+        <v>0.7702</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.4615</v>
+        <v>0.4659</v>
       </c>
       <c r="CI13" t="n">
         <v>0.5748</v>
@@ -5028,19 +5028,19 @@
         <v>94</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.7684</v>
+        <v>0.7702</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.2857</v>
+        <v>0.3055</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.6907</v>
+        <v>0.7007</v>
       </c>
       <c r="CN13" t="n">
         <v>0.6714</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="CP13" t="n">
         <v>0.1489</v>
@@ -5049,19 +5049,19 @@
         <v>461</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.7492</v>
+        <v>0.7498</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.3006</v>
+        <v>0.3167</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.6577</v>
+        <v>0.6636</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.5841</v>
+        <v>0.5725</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.7313</v>
+        <v>0.7548</v>
       </c>
       <c r="CW13" t="n">
         <v>0.2993</v>
@@ -5070,19 +5070,19 @@
         <v>552</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.7688</v>
+        <v>0.7689</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.3528</v>
+        <v>0.3659</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6873</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.6461</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.718</v>
+        <v>0.738</v>
       </c>
       <c r="DD13" t="n">
         <v>0.346</v>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -5140,46 +5140,46 @@
         <v>0.3362</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7746</v>
+        <v>0.7732</v>
       </c>
       <c r="N14" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6553</v>
+      </c>
+      <c r="T14" t="n">
         <v>0.0058</v>
       </c>
-      <c r="O14" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.0616</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.2243</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.6555</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.0101</v>
-      </c>
       <c r="U14" t="n">
-        <v>0.3759</v>
+        <v>0.3899</v>
       </c>
       <c r="V14" t="n">
         <v>0.0602</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3684</v>
+        <v>0.3724</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6924</v>
+        <v>0.6933</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6764</v>
+        <v>0.6646</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.7084</v>
+        <v>0.722</v>
       </c>
       <c r="AA14" t="n">
         <v>1</v>
@@ -5195,121 +5195,121 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>0.0318</v>
+        <v>0.0349</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0204</v>
+        <v>0.0339</v>
       </c>
       <c r="AF14" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>12.4419</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>195.4</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>23.8495</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12.4419</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>507.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>23.8495</v>
+      </c>
+      <c r="AT14" t="n">
         <v>0.5404</v>
       </c>
-      <c r="AG14" t="n">
-        <v>0.0142</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.0234</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.6976</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>240.8</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>11.3225</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>205</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>14.3701</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>115.2</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11.3225</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>498</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>14.3701</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.5258</v>
-      </c>
       <c r="AU14" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8469</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0107</v>
+        <v>0.0062</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.6297</v>
+        <v>0.6414</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0168</v>
+        <v>0.0065</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.3881</v>
+        <v>0.4062</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0178</v>
+        <v>0.004</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.6845</v>
+        <v>0.6937</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0078</v>
+        <v>0.002</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.7365</v>
+        <v>0.7439</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0083</v>
+        <v>0.0022</v>
       </c>
       <c r="BF14" t="n">
-        <v>187.2</v>
+        <v>192.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.4205</v>
+        <v>2.881</v>
       </c>
       <c r="BH14" t="n">
-        <v>110.2</v>
+        <v>107.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>7.5299</v>
+        <v>4.3359</v>
       </c>
       <c r="BJ14" t="n">
-        <v>168.8</v>
+        <v>163.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.4205</v>
+        <v>2.881</v>
       </c>
       <c r="BL14" t="n">
-        <v>592.8</v>
+        <v>595.4</v>
       </c>
       <c r="BM14" t="n">
-        <v>7.5299</v>
+        <v>4.3359</v>
       </c>
       <c r="BN14" t="n">
         <v>25</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.2976</v>
+        <v>0.3057</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.5502</v>
+        <v>0.5568</v>
       </c>
       <c r="BQ14" t="n">
         <v>0.5</v>
@@ -5330,19 +5330,19 @@
         <v>544</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.7165</v>
+        <v>0.7145</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.2099</v>
+        <v>0.2115</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.6186</v>
+        <v>0.6165</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.452</v>
+        <v>0.432</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.7851</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="CB14" t="n">
         <v>0.1838</v>
@@ -5351,19 +5351,19 @@
         <v>421</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.7067</v>
+        <v>0.7074</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.2785</v>
+        <v>0.2776</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.634</v>
+        <v>0.6342</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.7653</v>
+        <v>0.7579</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.5028</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="CI14" t="n">
         <v>0.5748</v>
@@ -5372,19 +5372,19 @@
         <v>94</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.8204</v>
+        <v>0.8222</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.3678</v>
+        <v>0.3636</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.7427</v>
+        <v>0.7359</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.7429</v>
+        <v>0.7143</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.7425</v>
+        <v>0.7575</v>
       </c>
       <c r="CP14" t="n">
         <v>0.1489</v>
@@ -5393,19 +5393,19 @@
         <v>461</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.7588</v>
+        <v>0.7598</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.3314</v>
+        <v>0.3526</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.6732</v>
+        <v>0.6814</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.6014</v>
+        <v>0.5913</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.7449</v>
+        <v>0.7715</v>
       </c>
       <c r="CW14" t="n">
         <v>0.2993</v>
@@ -5414,19 +5414,19 @@
         <v>552</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.7711</v>
+        <v>0.7709</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.359</v>
+        <v>0.3878</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.6842</v>
+        <v>0.6975</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.6377</v>
+        <v>0.6398</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.7307</v>
+        <v>0.7551</v>
       </c>
       <c r="DD14" t="n">
         <v>0.346</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -5484,46 +5484,46 @@
         <v>0.3362</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6874</v>
+        <v>0.6833</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0032</v>
+        <v>0.0033</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6273</v>
       </c>
       <c r="P15" t="n">
         <v>0.0039</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0548</v>
+        <v>0.056</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2924</v>
+        <v>0.3055</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5177</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0053</v>
+        <v>0.0074</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4859</v>
+        <v>0.4883</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0499</v>
+        <v>0.0586</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2903</v>
+        <v>0.2623</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6495</v>
+        <v>0.6353</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5837</v>
+        <v>0.5742</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.6964</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -5539,121 +5539,121 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>0.019</v>
+        <v>0.0368</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0159</v>
+        <v>0.0395</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.5095</v>
+        <v>0.4905</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0162</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0122</v>
+        <v>0.01</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0063</v>
+        <v>0.0043</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.671</v>
+        <v>0.6553</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0071</v>
+        <v>0.0144</v>
       </c>
       <c r="AL15" t="n">
-        <v>207.8</v>
+        <v>204.4</v>
       </c>
       <c r="AM15" t="n">
-        <v>6.7602</v>
+        <v>13.1072</v>
       </c>
       <c r="AN15" t="n">
-        <v>200.2</v>
+        <v>213.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>11.1669</v>
+        <v>27.7723</v>
       </c>
       <c r="AP15" t="n">
-        <v>148.2</v>
+        <v>151.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.7602</v>
+        <v>13.1072</v>
       </c>
       <c r="AR15" t="n">
-        <v>502.8</v>
+        <v>489.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.1669</v>
+        <v>27.7723</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.5702</v>
+        <v>0.5713</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0056</v>
+        <v>0.0117</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.7346</v>
+        <v>0.7183</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0056</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.5211</v>
+        <v>0.5068</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.0053</v>
+        <v>0.008</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2986</v>
+        <v>0.2821</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.0072</v>
+        <v>0.0123</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.6524</v>
+        <v>0.6448</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0036</v>
+        <v>0.0064</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.6793</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0038</v>
+        <v>0.0061</v>
       </c>
       <c r="BF15" t="n">
-        <v>203</v>
+        <v>203.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>2</v>
+        <v>4.1593</v>
       </c>
       <c r="BH15" t="n">
-        <v>186.6</v>
+        <v>198</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.9115</v>
+        <v>6</v>
       </c>
       <c r="BJ15" t="n">
-        <v>153</v>
+        <v>152.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>2</v>
+        <v>4.1593</v>
       </c>
       <c r="BL15" t="n">
-        <v>516.4</v>
+        <v>505</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.9115</v>
+        <v>6</v>
       </c>
       <c r="BN15" t="n">
         <v>25</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.4048</v>
+        <v>0.3037</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.5695</v>
+        <v>0.5749</v>
       </c>
       <c r="BQ15" t="n">
         <v>0.5</v>
@@ -5674,19 +5674,19 @@
         <v>544</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.637</v>
+        <v>0.6223</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.1637</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.378</v>
+        <v>0.342</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.8005</v>
+        <v>0.764</v>
       </c>
       <c r="CB15" t="n">
         <v>0.1838</v>
@@ -5695,19 +5695,19 @@
         <v>421</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.6279</v>
+        <v>0.6331</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.2037</v>
+        <v>0.2066</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.6015</v>
+        <v>0.6025</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.6711</v>
+        <v>0.6777</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5274</v>
       </c>
       <c r="CI15" t="n">
         <v>0.5748</v>
@@ -5716,19 +5716,19 @@
         <v>94</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.6355</v>
+        <v>0.5986</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.1454</v>
+        <v>0.1099</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.5977</v>
+        <v>0.5714</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.5429</v>
+        <v>0.4429</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.6525</v>
+        <v>0.7</v>
       </c>
       <c r="CP15" t="n">
         <v>0.1489</v>
@@ -5737,19 +5737,19 @@
         <v>461</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.6621</v>
+        <v>0.6847</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.2387</v>
+        <v>0.252</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.6166</v>
+        <v>0.6217</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.4406</v>
+        <v>0.4435</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.7926</v>
+        <v>0.8</v>
       </c>
       <c r="CW15" t="n">
         <v>0.2993</v>
@@ -5758,19 +5758,19 @@
         <v>552</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.6889</v>
+        <v>0.7005</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.2846</v>
+        <v>0.2715</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.6409</v>
+        <v>0.6333</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.5173</v>
+        <v>0.5026</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.7645</v>
+        <v>0.764</v>
       </c>
       <c r="DD15" t="n">
         <v>0.346</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -5828,46 +5828,46 @@
         <v>0.3362</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7015</v>
+        <v>0.7018</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0023</v>
+        <v>0.0033</v>
       </c>
       <c r="O16" t="n">
-        <v>0.647</v>
+        <v>0.641</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0034</v>
+        <v>0.0067</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0545</v>
+        <v>0.0608</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2705</v>
+        <v>0.3013</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5241</v>
+        <v>0.5285</v>
       </c>
       <c r="T16" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4455</v>
+        <v>0.4412</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0677</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2797</v>
+        <v>0.2748</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6465</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6287</v>
+        <v>0.6466</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.6643</v>
+        <v>0.6427</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -5883,121 +5883,121 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>0.0338</v>
+        <v>0.0328</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.4874</v>
+        <v>0.4785</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0128</v>
+        <v>0.0091</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0091</v>
+        <v>0.0134</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0045</v>
+        <v>0.0073</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.6523</v>
+        <v>0.644</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0114</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AL16" t="n">
-        <v>223.8</v>
+        <v>230.2</v>
       </c>
       <c r="AM16" t="n">
-        <v>12.0499</v>
+        <v>11.6919</v>
       </c>
       <c r="AN16" t="n">
-        <v>236</v>
+        <v>251.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>23.2056</v>
+        <v>18.2538</v>
       </c>
       <c r="AP16" t="n">
-        <v>132.2</v>
+        <v>125.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.0499</v>
+        <v>11.6919</v>
       </c>
       <c r="AR16" t="n">
-        <v>467</v>
+        <v>451.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>23.2056</v>
+        <v>18.2538</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.5775</v>
+        <v>0.5904</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0043</v>
+        <v>0.0111</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.7275</v>
+        <v>0.7101</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.0103</v>
+        <v>0.007</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.5178</v>
+        <v>0.5077</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0102</v>
+        <v>0.0076</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.2976</v>
+        <v>0.291</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.0132</v>
+        <v>0.0127</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.6525</v>
+        <v>0.6503</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.0064</v>
+        <v>0.0066</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.6771</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0076</v>
+        <v>0.006</v>
       </c>
       <c r="BF16" t="n">
-        <v>205.6</v>
+        <v>210.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.5166</v>
+        <v>3.9623</v>
       </c>
       <c r="BH16" t="n">
-        <v>191.6</v>
+        <v>203.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>7.2319</v>
+        <v>4.9193</v>
       </c>
       <c r="BJ16" t="n">
-        <v>150.4</v>
+        <v>145.8</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.5166</v>
+        <v>3.9623</v>
       </c>
       <c r="BL16" t="n">
-        <v>511.4</v>
+        <v>499.2</v>
       </c>
       <c r="BM16" t="n">
-        <v>7.2319</v>
+        <v>4.9193</v>
       </c>
       <c r="BN16" t="n">
         <v>25</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.3324</v>
+        <v>0.311</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.5815</v>
+        <v>0.578</v>
       </c>
       <c r="BQ16" t="n">
         <v>0.5</v>
@@ -6018,19 +6018,19 @@
         <v>544</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.653</v>
+        <v>0.6279</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.1403</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.5819</v>
+        <v>0.5567</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.422</v>
+        <v>0.404</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.7419</v>
+        <v>0.7095</v>
       </c>
       <c r="CB16" t="n">
         <v>0.1838</v>
@@ -6039,19 +6039,19 @@
         <v>421</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.6411</v>
+        <v>0.6552</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.2109</v>
+        <v>0.2446</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.6028</v>
+        <v>0.6175</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.7174</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.4883</v>
+        <v>0.4804</v>
       </c>
       <c r="CI16" t="n">
         <v>0.5748</v>
@@ -6060,19 +6060,19 @@
         <v>94</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.6377</v>
+        <v>0.6109</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.146</v>
+        <v>0.1104</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.5995</v>
+        <v>0.5746</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.5714</v>
+        <v>0.5143</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.635</v>
       </c>
       <c r="CP16" t="n">
         <v>0.1489</v>
@@ -6081,19 +6081,19 @@
         <v>461</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.6992</v>
+        <v>0.7166</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.244</v>
+        <v>0.2854</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.6259</v>
+        <v>0.6485</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.5174</v>
+        <v>0.5609</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7362</v>
       </c>
       <c r="CW16" t="n">
         <v>0.2993</v>
@@ -6102,19 +6102,19 @@
         <v>552</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.7191</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.275</v>
+        <v>0.3027</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.6408</v>
+        <v>0.6561</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.578</v>
+        <v>0.6136</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.7036</v>
+        <v>0.6986</v>
       </c>
       <c r="DD16" t="n">
         <v>0.346</v>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -6172,38 +6172,38 @@
         <v>0.6032999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6304</v>
+        <v>0.647</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0161</v>
+        <v>0.0126</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>0.7289</v>
+        <v>0.7246</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0108</v>
+        <v>0.0145</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6344</v>
+        <v>0.5451</v>
       </c>
       <c r="V17" t="n">
-        <v>0.112</v>
+        <v>0.1075</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1384</v>
+        <v>0.1788</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5669</v>
+        <v>0.586</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4124</v>
+        <v>0.586</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.5861</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -6219,121 +6219,121 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>0.0774</v>
+        <v>0.1866</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0825</v>
+        <v>0.1701</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.6964</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0255</v>
+        <v>0.0317</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0205</v>
+        <v>0.0242</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.535</v>
+        <v>0.586</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0162</v>
+        <v>0.0453</v>
       </c>
       <c r="AL17" t="n">
-        <v>153</v>
+        <v>217.4</v>
       </c>
       <c r="AM17" t="n">
-        <v>28.7315</v>
+        <v>69.2192</v>
       </c>
       <c r="AN17" t="n">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="AO17" t="n">
-        <v>20.1246</v>
+        <v>41.509</v>
       </c>
       <c r="AP17" t="n">
-        <v>218</v>
+        <v>153.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>28.7315</v>
+        <v>69.2192</v>
       </c>
       <c r="AR17" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="AS17" t="n">
-        <v>20.1246</v>
+        <v>41.509</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.7116</v>
+        <v>0.7062</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.0199</v>
+        <v>0.0161</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.4426</v>
+        <v>0.4869</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0254</v>
+        <v>0.031</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.66</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0122</v>
+        <v>0.0106</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.1583</v>
+        <v>0.1956</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0331</v>
+        <v>0.0228</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0162</v>
+        <v>0.0118</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.6049</v>
+        <v>0.6192</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.0158</v>
+        <v>0.0094</v>
       </c>
       <c r="BF17" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.3824</v>
+        <v>5.9582</v>
       </c>
       <c r="BH17" t="n">
-        <v>136</v>
+        <v>125.2</v>
       </c>
       <c r="BI17" t="n">
-        <v>6.2048</v>
+        <v>7.5631</v>
       </c>
       <c r="BJ17" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BK17" t="n">
-        <v>7.3824</v>
+        <v>5.9582</v>
       </c>
       <c r="BL17" t="n">
-        <v>108</v>
+        <v>118.8</v>
       </c>
       <c r="BM17" t="n">
-        <v>6.2048</v>
+        <v>7.5631</v>
       </c>
       <c r="BN17" t="n">
         <v>25</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.3854</v>
+        <v>0.414</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.8165</v>
+        <v>0.7472</v>
       </c>
       <c r="BQ17" t="n">
         <v>0.5</v>
